--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45875.5</v>
+        <v>45875.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>3.02</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
         <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="M10" t="n">
         <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
         <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45875.45833333334</v>
+        <v>45875.25</v>
       </c>
     </row>
     <row r="3">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2267,43 +2267,43 @@
         <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB14" t="n">
         <v>1.57</v>
@@ -2312,22 +2312,22 @@
         <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2399,43 +2399,43 @@
         <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
@@ -2444,22 +2444,22 @@
         <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="P14" t="n">
-        <v>17.25</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T14" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P15" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.27</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P15" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -941,73 +941,73 @@
         <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>3.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P6" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>1.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>17.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2003,43 +2003,43 @@
         <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
         <v>1.67</v>
@@ -2048,22 +2048,22 @@
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2531,49 +2531,49 @@
         <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
@@ -2582,16 +2582,16 @@
         <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="M17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
         <v>3.1</v>
@@ -2795,67 +2795,67 @@
         <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3059,67 +3059,67 @@
         <v>2.27</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,37 +1202,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>4.95</v>
+        <v>4.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1244,34 +1244,34 @@
         <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH6" t="n">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,28 +1334,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>16.25</v>
+        <v>17.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
         <v>2.25</v>
@@ -1370,7 +1370,7 @@
         <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
         <v>15</v>
@@ -1379,10 +1379,10 @@
         <v>1.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
         <v>2.3</v>
@@ -1394,13 +1394,13 @@
         <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AI7" t="n">
         <v>1.2</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,37 +1466,37 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="P8" t="n">
-        <v>18.75</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>4.55</v>
+        <v>4.95</v>
       </c>
       <c r="W8" t="n">
         <v>1.15</v>
@@ -1508,34 +1508,34 @@
         <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>17.25</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>2.25</v>
@@ -1772,28 +1772,28 @@
         <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="n">
         <v>4.33</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,22 +1862,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
         <v>1.29</v>
@@ -1898,37 +1898,37 @@
         <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
         <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI11" t="n">
         <v>1.2</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P14" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.27</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P14" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
-        <v>17.25</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T15" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AG15" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45875.25</v>
+        <v>45875.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.95</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>15.5</v>
+        <v>17.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
         <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,28 +1334,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="P7" t="n">
-        <v>17.25</v>
+        <v>16.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
         <v>2.25</v>
@@ -1370,7 +1370,7 @@
         <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>15</v>
@@ -1379,10 +1379,10 @@
         <v>1.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
         <v>2.3</v>
@@ -1394,13 +1394,13 @@
         <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI7" t="n">
         <v>1.2</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
         <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.4</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.57</v>
       </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG10" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="P11" t="n">
-        <v>16.25</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.29</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AA11" t="n">
         <v>3.4</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -962,13 +962,13 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="U4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -998,10 +998,10 @@
         <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="n">
         <v>4.33</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="P5" t="n">
-        <v>17.25</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.29</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AA5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>18.75</v>
+        <v>15.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
         <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.52</v>
+        <v>4.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,64 +1334,64 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="P7" t="n">
-        <v>16.25</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.57</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
         <v>1.5</v>
@@ -1400,10 +1400,10 @@
         <v>2.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH8" t="n">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,73 +1598,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.95</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
         <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
         <v>1.2</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>15.5</v>
+        <v>16.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>6.25</v>
+        <v>5.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2012,19 +2012,19 @@
         <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
@@ -2048,22 +2048,22 @@
         <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.15</v>
+        <v>4.98</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2144,40 +2144,40 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
         <v>1.9</v>
@@ -2186,16 +2186,16 @@
         <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="P14" t="n">
-        <v>17.25</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T14" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P15" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.27</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P15" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
         <v>3.6</v>
@@ -2549,13 +2549,13 @@
         <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
@@ -2564,16 +2564,16 @@
         <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
@@ -2582,10 +2582,10 @@
         <v>1.67</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH16" t="n">
         <v>3.25</v>
@@ -2672,58 +2672,58 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2804,28 +2804,28 @@
         <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
         <v>2.46</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="Z18" t="n">
         <v>1.22</v>
@@ -3086,7 +3086,7 @@
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>8.5</v>
@@ -3101,7 +3101,7 @@
         <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AD20" t="n">
         <v>3.3</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.63</v>
       </c>
       <c r="O4" t="n">
         <v>1.61</v>
@@ -956,16 +956,16 @@
         <v>2.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T4" t="n">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="U4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
         <v>5.5</v>
@@ -977,31 +977,31 @@
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
         <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH4" t="n">
         <v>4.33</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>3.64</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>4.03</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>1.76</v>
       </c>
       <c r="O5" t="n">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.39</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>3.84</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>3.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
         <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD6" t="n">
         <v>2.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.65</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>3.51</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
@@ -1373,37 +1373,37 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.6</v>
+        <v>12.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="P8" t="n">
-        <v>18.75</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>2.39</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>6.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.28</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="O9" t="n">
         <v>1.51</v>
@@ -1616,55 +1616,55 @@
         <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="U9" t="n">
         <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="Z9" t="n">
         <v>1.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
         <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AE9" t="n">
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="AI9" t="n">
         <v>1.2</v>
@@ -1748,58 +1748,58 @@
         <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AC10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD10" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AF10" t="n">
         <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>4.64</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.54</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>18.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
         <v>1.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.63</v>
+        <v>2.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>1.67</v>
@@ -2012,25 +2012,25 @@
         <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
         <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
         <v>12</v>
@@ -2039,31 +2039,31 @@
         <v>1.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.98</v>
+        <v>5.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2126,40 +2126,40 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
         <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
@@ -2168,22 +2168,22 @@
         <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
         <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
         <v>1.37</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.8</v>
@@ -2543,55 +2543,55 @@
         <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
         <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z16" t="n">
         <v>1.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
         <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="n">
         <v>3.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.52</v>
@@ -2804,52 +2804,52 @@
         <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="T18" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
         <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
         <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AB18" t="n">
         <v>1.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AE18" t="n">
         <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="n">
         <v>4.8</v>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
         <v>2.28</v>
@@ -3071,7 +3071,7 @@
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
         <v>2.98</v>
@@ -3080,34 +3080,34 @@
         <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
         <v>3.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
         <v>1.67</v>
@@ -3116,7 +3116,7 @@
         <v>1.91</v>
       </c>
       <c r="AH20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AI20" t="n">
         <v>1.08</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.64</v>
+        <v>4.64</v>
       </c>
       <c r="M5" t="n">
-        <v>4.03</v>
+        <v>4.54</v>
       </c>
       <c r="N5" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="O5" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87</v>
+        <v>3.51</v>
       </c>
       <c r="N6" t="n">
-        <v>3.74</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>12.3</v>
       </c>
       <c r="Z6" t="n">
         <v>1.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
         <v>2.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.51</v>
+        <v>3.99</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>3.58</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>15.5</v>
+        <v>17.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
         <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>16.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
-        <v>6.15</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="M9" t="n">
-        <v>3.99</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="P9" t="n">
-        <v>17.25</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD9" t="n">
         <v>3.1</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.31</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>3.64</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>4.03</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="P10" t="n">
-        <v>16.25</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
         <v>2.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
         <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.64</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>4.54</v>
+        <v>3.87</v>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>3.74</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>18.75</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA11" t="n">
         <v>4.5</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="O13" t="n">
         <v>1.77</v>
@@ -2180,10 +2180,10 @@
         <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
         <v>1.37</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>1.61</v>
@@ -965,49 +965,49 @@
         <v>2.39</v>
       </c>
       <c r="U4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.4</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD4" t="n">
         <v>2.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.64</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>4.54</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.53</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P5" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="M6" t="n">
-        <v>3.51</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>15.5</v>
+        <v>17.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
         <v>3.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
         <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>17.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.3</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.31</v>
+        <v>4.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="P8" t="n">
-        <v>16.25</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.39</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>2.21</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>4.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.1</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.64</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.03</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>16.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
         <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.15</v>
@@ -1769,34 +1769,34 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF10" t="n">
         <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="AI10" t="n">
         <v>1.22</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>5.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.87</v>
+        <v>4.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>1.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>18.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.57</v>
       </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>1.67</v>
@@ -2012,7 +2012,7 @@
         <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -2021,19 +2021,19 @@
         <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
         <v>1.22</v>
@@ -2042,10 +2042,10 @@
         <v>3.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
         <v>2.75</v>
@@ -2054,16 +2054,16 @@
         <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="M16" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.8</v>
@@ -2540,19 +2540,19 @@
         <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
         <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.18</v>
@@ -2576,10 +2576,10 @@
         <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF16" t="n">
         <v>1.4</v>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,31 +1070,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.95</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>1.55</v>
@@ -1106,40 +1106,40 @@
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AE5" t="n">
         <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>17.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>3.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="P7" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AF7" t="n">
         <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>16.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>3.87</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>2.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA9" t="n">
         <v>3.3</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.85</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>16.25</v>
+        <v>18.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
         <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.2</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>18.75</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA11" t="n">
         <v>4.5</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.75</v>
@@ -2672,10 +2672,10 @@
         <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
         <v>2.9</v>
@@ -2687,10 +2687,10 @@
         <v>7</v>
       </c>
       <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>8.5</v>
@@ -2699,19 +2699,19 @@
         <v>1.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AB17" t="n">
         <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="n">
         <v>3.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
         <v>1.87</v>
@@ -2723,7 +2723,7 @@
         <v>6.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.52</v>
@@ -2804,52 +2804,52 @@
         <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
         <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="Z18" t="n">
         <v>1.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AB18" t="n">
         <v>1.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
         <v>2.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH18" t="n">
         <v>4.8</v>
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="O20" t="n">
         <v>2.28</v>
@@ -3068,10 +3068,10 @@
         <v>1.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
         <v>2.98</v>
@@ -3086,22 +3086,22 @@
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD20" t="n">
         <v>3.3</v>
@@ -3119,7 +3119,7 @@
         <v>6.9</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="P5" t="n">
-        <v>17.25</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD5" t="n">
         <v>3.1</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.28</v>
+        <v>6.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>16.25</v>
+        <v>18.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
         <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>17.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>4.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>18.75</v>
+        <v>16.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45875.54166666666</v>
+        <v>45875.5</v>
       </c>
     </row>
     <row r="5">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="O5" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>15.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.1</v>
+        <v>12.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45875.58333333334</v>
+        <v>45875.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
         <v>1.88</v>
@@ -1220,40 +1220,40 @@
         <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
         <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="Z6" t="n">
         <v>1.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
         <v>2.5</v>
@@ -1262,16 +1262,16 @@
         <v>1.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH7" t="n">
         <v>3.3</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AI7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.2</v>
+        <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>3.87</v>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>3.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>1.59</v>
       </c>
       <c r="P8" t="n">
-        <v>18.75</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
         <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>13.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>2.48</v>
       </c>
       <c r="P9" t="n">
-        <v>17.25</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.28</v>
+        <v>3.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
         <v>3.65</v>
@@ -1742,64 +1742,64 @@
         <v>1.95</v>
       </c>
       <c r="P10" t="n">
-        <v>16.25</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.87</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,31 +1862,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>3.64</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>16.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
         <v>1.55</v>
@@ -1898,40 +1898,40 @@
         <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>12.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>17.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45875.625</v>
+        <v>45875.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2085,27 +2085,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,77 +2126,77 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.72</v>
       </c>
-      <c r="V13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AG13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.12</v>
       </c>
-      <c r="AA13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>45875.64583333334</v>
+        <v>45875.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>8.25</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.83</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45875.66666666666</v>
+        <v>45875.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.29</v>
       </c>
       <c r="O15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>17.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.65</v>
+        <v>3.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45875.66666666666</v>
+        <v>45875.625</v>
       </c>
     </row>
     <row r="16">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>15.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45875.67708333334</v>
+        <v>45875.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
         <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45875.83333333334</v>
+        <v>45875.64583333334</v>
       </c>
     </row>
     <row r="18">
@@ -2745,27 +2745,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
       <c r="P18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="n">
         <v>4.8</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45875.85416666666</v>
+        <v>45875.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45875.91666666666</v>
+        <v>45875.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -3009,129 +3009,789 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P20" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL20" s="3" t="n">
+        <v>45875.66666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL21" s="3" t="n">
+        <v>45875.67708333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL22" s="3" t="n">
+        <v>45875.83333333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Miami FC II</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>45875.85416666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL24" s="3" t="n">
+        <v>45875.91666666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Monterey Bay</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Tulsa Roughnecks</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="L25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O25" t="n">
         <v>2.28</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P25" t="n">
         <v>9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q25" t="n">
         <v>1.77</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.75</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="T25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH25" t="n">
         <v>7.4</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+      <c r="AI25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="n">
         <v>45875.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>4.04</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.61</v>
@@ -1094,22 +1094,22 @@
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
         <v>1.16</v>
@@ -1121,7 +1121,7 @@
         <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
         <v>2.6</v>
@@ -1130,16 +1130,16 @@
         <v>1.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
         <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.45</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.48</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE6" t="n">
         <v>1.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.5</v>
+        <v>2.51</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>18.75</v>
+        <v>15.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1.2</v>
       </c>
-      <c r="S7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.26</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="O8" t="n">
         <v>1.59</v>
@@ -1484,10 +1484,10 @@
         <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
         <v>2.25</v>
@@ -1505,37 +1505,37 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.8</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>6.04</v>
       </c>
       <c r="M9" t="n">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
         <v>18</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>17</v>
       </c>
       <c r="Z9" t="n">
         <v>1.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>17.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.5</v>
       </c>
-      <c r="V10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
         <v>1.95</v>
@@ -1880,58 +1880,58 @@
         <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="U11" t="n">
         <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
         <v>12.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.52</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="n">
         <v>4.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="P12" t="n">
-        <v>17.25</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="T12" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>9.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>3.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>3.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.39</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AA13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AH13" t="n">
         <v>3.5</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.29</v>
+        <v>2.98</v>
       </c>
       <c r="O15" t="n">
         <v>1.67</v>
@@ -2408,58 +2408,58 @@
         <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AE15" t="n">
         <v>1.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>1.77</v>
@@ -2672,58 +2672,58 @@
         <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AB17" t="n">
         <v>1.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
         <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>17.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>17.25</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>1.8</v>
@@ -3200,58 +3200,58 @@
         <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
         <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>1.75</v>
@@ -3332,19 +3332,19 @@
         <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
         <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U22" t="n">
         <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
         <v>1.06</v>
@@ -3356,31 +3356,31 @@
         <v>8.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
         <v>3.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI22" t="n">
         <v>1.04</v>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.52</v>
@@ -3464,58 +3464,58 @@
         <v>2.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
         <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
         <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="n">
         <v>4.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
         <v>2.28</v>
@@ -3728,58 +3728,58 @@
         <v>1.77</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
         <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U25" t="n">
         <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AB25" t="n">
         <v>1.97</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD25" t="n">
         <v>3.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG25" t="n">
         <v>1.91</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="M2" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.72</v>
@@ -692,10 +692,10 @@
         <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
         <v>2.8</v>
@@ -704,10 +704,10 @@
         <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
@@ -719,13 +719,13 @@
         <v>1.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AD2" t="n">
         <v>3.34</v>
@@ -734,13 +734,13 @@
         <v>1.24</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AI2" t="n">
         <v>1.05</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.04</v>
+        <v>4.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
         <v>2.78</v>
@@ -824,58 +824,58 @@
         <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>1.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
         <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.85</v>
+        <v>7.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.13</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AA6" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,61 +1334,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.51</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="O7" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="P7" t="n">
-        <v>15.5</v>
+        <v>16.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="W7" t="n">
         <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>12.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AE7" t="n">
         <v>1.5</v>
@@ -1397,13 +1397,13 @@
         <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.04</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P9" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P9" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="W9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.18</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.89</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.07</v>
+        <v>2.51</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,61 +1730,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>2.47</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>17.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AE10" t="n">
         <v>1.5</v>
@@ -1793,10 +1793,10 @@
         <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AI10" t="n">
         <v>1.2</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
         <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>16.25</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.7</v>
+        <v>6.04</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
         <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
         <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="P16" t="n">
-        <v>8.25</v>
+        <v>16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AG16" t="n">
         <v>2.75</v>
       </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.19</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.75</v>
       </c>
-      <c r="O17" t="n">
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.77</v>
       </c>
-      <c r="P17" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.98</v>
+        <v>3.55</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.15</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
         <v>8</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="Z3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
         <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AE4" t="n">
         <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
         <v>1.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="O5" t="n">
         <v>1.61</v>
@@ -1088,10 +1088,10 @@
         <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
         <v>2.45</v>
@@ -1100,13 +1100,13 @@
         <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
         <v>13</v>
@@ -1115,31 +1115,31 @@
         <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
         <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
         <v>2.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF5" t="n">
         <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.7</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>3.77</v>
       </c>
       <c r="O6" t="n">
-        <v>2.48</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>17.25</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.55</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
         <v>1.95</v>
@@ -1352,10 +1352,10 @@
         <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
         <v>2.42</v>
@@ -1367,7 +1367,7 @@
         <v>4.95</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
@@ -1379,28 +1379,28 @@
         <v>1.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
         <v>1.22</v>
@@ -1469,10 +1469,10 @@
         <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="N8" t="n">
-        <v>3.74</v>
+        <v>3.67</v>
       </c>
       <c r="O8" t="n">
         <v>1.59</v>
@@ -1484,16 +1484,16 @@
         <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
         <v>4.5</v>
@@ -1511,28 +1511,28 @@
         <v>1.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AF8" t="n">
         <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AI8" t="n">
         <v>1.2</v>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>17.25</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH9" t="n">
         <v>5</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="O10" t="n">
         <v>1.88</v>
@@ -1748,16 +1748,16 @@
         <v>1.97</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
         <v>2.43</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
         <v>5.25</v>
@@ -1769,37 +1769,37 @@
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
         <v>2.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
         <v>2.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA11" t="n">
         <v>5.5</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>5.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>1.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1.74</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>18.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.39</v>
+        <v>1.43</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.85</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.04</v>
+        <v>1.89</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="P13" t="n">
-        <v>18.75</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>2.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.5</v>
+        <v>3.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.89</v>
+        <v>1.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.3</v>
+        <v>5.35</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.98</v>
+        <v>3.29</v>
       </c>
       <c r="O15" t="n">
         <v>1.67</v>
@@ -2411,19 +2411,19 @@
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
         <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
         <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2435,31 +2435,31 @@
         <v>1.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
         <v>2.8</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="n">
         <v>5.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.77</v>
       </c>
-      <c r="P16" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
+        <v>3.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
-        <v>8.25</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AG17" t="n">
         <v>2.75</v>
       </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
-        <v>17.25</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>4.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>17.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.95</v>
+        <v>4.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="O21" t="n">
         <v>1.8</v>
@@ -3200,58 +3200,58 @@
         <v>1.95</v>
       </c>
       <c r="R21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.28</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.75</v>
@@ -3335,22 +3335,22 @@
         <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
         <v>2.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
         <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
         <v>8.5</v>
@@ -3359,28 +3359,28 @@
         <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
         <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI22" t="n">
         <v>1.04</v>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.52</v>
@@ -3467,10 +3467,10 @@
         <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
         <v>1.48</v>
@@ -3479,7 +3479,7 @@
         <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -3491,13 +3491,13 @@
         <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD23" t="n">
         <v>2.6</v>
@@ -3506,7 +3506,7 @@
         <v>1.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG23" t="n">
         <v>2.1</v>
@@ -3515,7 +3515,7 @@
         <v>4.8</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
         <v>2.28</v>
@@ -3731,13 +3731,13 @@
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
         <v>2.95</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
         <v>7.7</v>
@@ -3749,37 +3749,37 @@
         <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z25" t="n">
         <v>1.36</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
         <v>1.97</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
         <v>3.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
         <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.15</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
         <v>8</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" t="n">
         <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
         <v>1.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.72</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P6" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AC6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH6" t="n">
         <v>5</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AI6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="P7" t="n">
-        <v>16.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="U7" t="n">
         <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
         <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.76</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.87</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3.67</v>
+        <v>1.41</v>
       </c>
       <c r="O8" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>18.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.58</v>
       </c>
-      <c r="V8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA9" t="n">
         <v>5.5</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.17</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,64 +1730,64 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.87</v>
       </c>
       <c r="N10" t="n">
-        <v>2.48</v>
+        <v>3.67</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="T10" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V10" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" t="n">
         <v>1.53</v>
@@ -1796,10 +1796,10 @@
         <v>2.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,52 +1862,52 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.94</v>
+        <v>3.64</v>
       </c>
       <c r="N11" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>18</v>
+        <v>16.25</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.55</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>12.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB11" t="n">
         <v>1.52</v>
@@ -1922,13 +1922,13 @@
         <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
         <v>1.22</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.5</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.41</v>
+        <v>3.77</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
-        <v>18.75</v>
+        <v>17.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.18</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AA12" t="n">
-        <v>5.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="P19" t="n">
-        <v>17.25</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>17.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -695,55 +695,55 @@
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="T2" t="n">
         <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.07</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.05</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.15</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
         <v>8</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="Z3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
         <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AA4" t="n">
         <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>1.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1088,25 +1088,25 @@
         <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
         <v>13</v>
@@ -1124,22 +1124,22 @@
         <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
         <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>16.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>4.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.47</v>
+        <v>3.94</v>
       </c>
       <c r="N7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O7" t="n">
         <v>2.48</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.88</v>
-      </c>
       <c r="P7" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>1.89</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>3.56</v>
       </c>
       <c r="N8" t="n">
-        <v>1.41</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="P8" t="n">
-        <v>18.75</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>2.39</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AH8" t="n">
-        <v>3.3</v>
+        <v>5.98</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="N9" t="n">
-        <v>1.77</v>
+        <v>3.67</v>
       </c>
       <c r="O9" t="n">
-        <v>2.48</v>
+        <v>1.59</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
         <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.76</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.87</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.67</v>
+        <v>1.41</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>18.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
         <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>16.25</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
         <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N12" t="n">
-        <v>3.77</v>
+        <v>2.48</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>17.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="Z12" t="n">
         <v>1.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
         <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>17.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.78</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.44</v>
+        <v>4.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2408,19 +2408,19 @@
         <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
         <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="W15" t="n">
         <v>1.12</v>
@@ -2429,13 +2429,13 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AB15" t="n">
         <v>1.75</v>
@@ -2450,13 +2450,13 @@
         <v>1.36</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AI15" t="n">
         <v>1.12</v>
@@ -2672,34 +2672,34 @@
         <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB17" t="n">
         <v>1.42</v>
@@ -2714,16 +2714,16 @@
         <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3200,22 +3200,22 @@
         <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
@@ -3224,10 +3224,10 @@
         <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
         <v>1.41</v>
@@ -3242,13 +3242,13 @@
         <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AI21" t="n">
         <v>1.25</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="O22" t="n">
         <v>1.75</v>
@@ -3332,34 +3332,34 @@
         <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
         <v>2.05</v>
@@ -3368,19 +3368,19 @@
         <v>1.68</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AE22" t="n">
         <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI22" t="n">
         <v>1.04</v>
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.52</v>
@@ -3464,19 +3464,19 @@
         <v>2.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
         <v>1.12</v>
@@ -3485,13 +3485,13 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="Z23" t="n">
         <v>1.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
         <v>1.7</v>
@@ -3503,13 +3503,13 @@
         <v>2.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH23" t="n">
         <v>4.8</v>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O25" t="n">
         <v>2.28</v>
@@ -3740,7 +3740,7 @@
         <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.08</v>
@@ -3749,13 +3749,13 @@
         <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
         <v>1.36</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AB25" t="n">
         <v>1.97</v>
@@ -3764,22 +3764,22 @@
         <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF25" t="n">
         <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AA3" t="n">
         <v>2.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.15</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
         <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
         <v>1.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,52 +1202,52 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.64</v>
+        <v>3.94</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="P6" t="n">
-        <v>16.25</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AB6" t="n">
         <v>1.52</v>
@@ -1262,16 +1262,16 @@
         <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,52 +1334,52 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.94</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="P7" t="n">
-        <v>18</v>
+        <v>16.25</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.55</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V7" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB7" t="n">
         <v>1.52</v>
@@ -1394,16 +1394,16 @@
         <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.98</v>
+        <v>4.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.87</v>
+        <v>4.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.67</v>
+        <v>1.41</v>
       </c>
       <c r="O9" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>18.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="W9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.12</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>1.76</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>3.87</v>
       </c>
       <c r="N10" t="n">
-        <v>1.41</v>
+        <v>3.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>18.75</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.3</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,73 +1994,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.47</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="P12" t="n">
-        <v>15.5</v>
+        <v>17.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AA12" t="n">
         <v>4.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG12" t="n">
         <v>2.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AI12" t="n">
         <v>1.18</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="P13" t="n">
-        <v>17.25</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD13" t="n">
         <v>3.1</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.1</v>
+        <v>5.98</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="P16" t="n">
-        <v>8.25</v>
+        <v>16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.77</v>
+        <v>2.73</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.55</v>
+        <v>1.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="O17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.77</v>
       </c>
-      <c r="P17" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>3.55</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.48</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>17.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.95</v>
+        <v>4.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.55</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P19" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.08</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V19" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.98</v>
+        <v>4.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,76 +3050,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>17.25</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T20" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="M24" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3596,58 +3596,58 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="M6" t="n">
-        <v>3.94</v>
+        <v>3.56</v>
       </c>
       <c r="N6" t="n">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>2.39</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.65</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.5</v>
+        <v>5.98</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.16</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>16.25</v>
+        <v>18.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH7" t="n">
         <v>3.3</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AI7" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.47</v>
+        <v>3.94</v>
       </c>
       <c r="N8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O8" t="n">
         <v>2.48</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.88</v>
-      </c>
       <c r="P8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.4</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>18.75</v>
+        <v>16.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" t="n">
         <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="N12" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>17.25</v>
+        <v>17</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.15</v>
       </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AA12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>1.55</v>
       </c>
       <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.98</v>
+        <v>4.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL25"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -657,20 +652,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -683,79 +678,76 @@
         <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.72</v>
+        <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="T2" t="n">
         <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>3.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
         <v>3.2</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.75</v>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.5</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45875.45833333334</v>
       </c>
     </row>
@@ -770,26 +762,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -802,92 +794,89 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45875.5</v>
       </c>
     </row>
@@ -902,124 +891,121 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['2', '5']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['25', '45+6', '85', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.33</v>
       </c>
-      <c r="V4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>1.14</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45875.5</v>
       </c>
     </row>
@@ -1053,105 +1039,102 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M5" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>3.51</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['24', '42']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.61</v>
       </c>
-      <c r="P5" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="AJ5" t="n">
         <v>2.4</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AK5" s="3" t="n">
         <v>45875.54166666666</v>
       </c>
     </row>
@@ -1176,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1198,92 +1181,89 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="M6" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['47', '50']</t>
+        </is>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.98</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -1320,102 +1300,99 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8</v>
+        <v>4.92</v>
       </c>
       <c r="N7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="O7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['34', '67']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.88</v>
       </c>
-      <c r="P7" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="AJ7" t="n">
         <v>1.43</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AK7" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -1449,105 +1426,102 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>2.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['12', '76']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['39', '64']</t>
+        </is>
       </c>
       <c r="AG8" t="n">
-        <v>2.49</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -1572,114 +1546,111 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>16.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>4.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
-        <v>4.35</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>3.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>1.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.14</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.7</v>
+        <v>2.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>1.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['67', '82']</t>
+        </is>
       </c>
       <c r="AG9" t="n">
-        <v>2.57</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -1694,29 +1665,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1726,92 +1697,89 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.77</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>17.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>4.95</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.52</v>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.1</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -1826,124 +1794,121 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
         <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>4.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.22</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['79', '85']</t>
+        </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -1990,92 +1955,89 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.59</v>
       </c>
-      <c r="P12" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="AJ12" t="n">
         <v>2.4</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AK12" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -2100,114 +2062,111 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>2.48</v>
+        <v>4.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>4.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>5.05</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>4.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.4</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.18</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['15', '58']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2.3</v>
       </c>
-      <c r="AH13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45875.58333333334</v>
       </c>
     </row>
@@ -2254,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2267,13 +2226,13 @@
         <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>8.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -2288,58 +2247,55 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45875.60416666666</v>
       </c>
     </row>
@@ -2373,105 +2329,102 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N15" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.25</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="T15" t="n">
         <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>6.1</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.66</v>
+        <v>2.07</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
       </c>
       <c r="AG15" t="n">
-        <v>2.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45875.625</v>
       </c>
     </row>
@@ -2486,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,114 +2449,111 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.46</v>
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['9', '51', '73']</t>
+        </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
         <v>45875.64583333334</v>
       </c>
     </row>
@@ -2618,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,114 +2578,111 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['39', '60', '75', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AK17" s="3" t="n">
         <v>45875.64583333334</v>
       </c>
     </row>
@@ -2760,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2782,92 +2729,89 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.68</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>17.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>3.98</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>2.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.51</v>
+        <v>2.25</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['53', '88']</t>
+        </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.39</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45875.66666666666</v>
       </c>
     </row>
@@ -2882,124 +2826,121 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.45</v>
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['19', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45875.66666666666</v>
       </c>
     </row>
@@ -3014,124 +2955,121 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.55</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P20" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.08</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>4.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.18</v>
       </c>
-      <c r="AA20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45875.66666666666</v>
       </c>
     </row>
@@ -3165,10 +3103,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3178,92 +3116,89 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.8</v>
       </c>
-      <c r="P21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="AJ21" t="n">
         <v>1.95</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
+      <c r="AK21" s="3" t="n">
         <v>45875.67708333334</v>
       </c>
     </row>
@@ -3297,7 +3232,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -3310,92 +3245,89 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="M22" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
         <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.6</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.75</v>
       </c>
-      <c r="AH22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
+      <c r="AJ22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45875.83333333334</v>
       </c>
     </row>
@@ -3429,7 +3361,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3442,92 +3374,89 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="P23" t="n">
-        <v>13.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>4.72</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>5.75</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>3.86</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.4</v>
+        <v>1.68</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AD23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['46', '73']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.6</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AK23" s="3" t="n">
         <v>45875.85416666666</v>
       </c>
     </row>
@@ -3561,39 +3490,39 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="N24" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R24" t="n">
         <v>1.27</v>
@@ -3602,64 +3531,61 @@
         <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="U24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.16</v>
+        <v>2.26</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['45+2', '80']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['29', '45+3', '47', '87']</t>
+        </is>
       </c>
       <c r="AG24" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>4.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45875.91666666666</v>
       </c>
     </row>
@@ -3693,20 +3619,20 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3719,79 +3645,76 @@
         <v>2.06</v>
       </c>
       <c r="O25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['51', '59']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['12', '71', '86']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI25" t="n">
         <v>2.28</v>
       </c>
-      <c r="P25" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="AJ25" t="n">
         <v>1.77</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AK25" s="3" t="n">
         <v>45875.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-06.xlsx
+++ b/jogos_2025-08-06.xlsx
@@ -762,35 +762,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['2', '5']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '45+6', '85', '90+1']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45875.5</v>
@@ -891,35 +891,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['2', '5']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['25', '45+6', '85', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45875.5</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.97</v>
+        <v>1.98</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.2</v>
       </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>4.7</v>
+        <v>3.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['47', '50']</t>
+          <t>['67', '82']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>2.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45875.58333333334</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="W7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.45</v>
       </c>
-      <c r="O7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['15', '58']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['34', '67']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.43</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45875.58333333334</v>
@@ -1407,35 +1407,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['12', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['39', '64']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45875.58333333334</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.99</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="U9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AA9" t="n">
         <v>2.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['67', '82']</t>
+          <t>['79', '85']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45875.58333333334</v>
@@ -1665,35 +1665,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['12', '76']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['39', '64']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.22</v>
       </c>
-      <c r="X10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AI10" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45875.58333333334</v>
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.6</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['79', '85']</t>
+          <t>['34', '67']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>2.71</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45875.58333333334</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.64</v>
+        <v>2.97</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>4.55</v>
+        <v>2.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.72</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="Y13" t="n">
         <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['15', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '50']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.51</v>
+        <v>1.88</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45875.58333333334</v>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45875.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['39', '60', '75', '90+1']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['9', '51', '73']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45875.64583333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA17" t="n">
         <v>3.55</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['39', '60', '75', '90+1']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['9', '51', '73']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45875.64583333334</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>2.47</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>3.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '90+1']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['53', '88']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45875.66666666666</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['19', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['53', '88']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45875.66666666666</v>
